--- a/data/清远/信用卡对账/PMS报表.xlsx
+++ b/data/清远/信用卡对账/PMS报表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\larfe\Qingyuan\data\清远\信用卡对账\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C1BF43-5F4C-4553-A14F-70509FC159D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12200"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PMS报表" sheetId="1" r:id="rId1"/>
@@ -236,14 +242,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,352 +252,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -605,311 +275,25 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1194,21 +578,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G84"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5" customWidth="1"/>
+    <col min="1" max="1" width="17.453125" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="6" max="6" width="50.3727272727273" customWidth="1"/>
+    <col min="6" max="6" width="50.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1231,7 +615,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9005</v>
       </c>
@@ -1251,7 +635,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2607210001</v>
       </c>
@@ -1271,7 +655,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2607210002</v>
       </c>
@@ -1291,7 +675,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2607210002</v>
       </c>
@@ -1311,7 +695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2607210002</v>
       </c>
@@ -1331,7 +715,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2607210003</v>
       </c>
@@ -1351,7 +735,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2607210003</v>
       </c>
@@ -1371,7 +755,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2607210005</v>
       </c>
@@ -1391,7 +775,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2607210006</v>
       </c>
@@ -1411,7 +795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2607210007</v>
       </c>
@@ -1431,7 +815,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2607210011</v>
       </c>
@@ -1451,7 +835,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2607210012</v>
       </c>
@@ -1471,7 +855,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2607210013</v>
       </c>
@@ -1491,7 +875,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2607210013</v>
       </c>
@@ -1511,7 +895,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2607210014</v>
       </c>
@@ -1531,7 +915,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2607210014</v>
       </c>
@@ -1551,7 +935,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1571,7 +955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2607210017</v>
       </c>
@@ -1591,7 +975,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2607210018</v>
       </c>
@@ -1611,7 +995,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2607210019</v>
       </c>
@@ -1631,7 +1015,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2607210023</v>
       </c>
@@ -1651,7 +1035,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1671,7 +1055,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2607210028</v>
       </c>
@@ -1691,7 +1075,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2607210029</v>
       </c>
@@ -1711,7 +1095,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2607210030</v>
       </c>
@@ -1725,13 +1109,13 @@
         <v>7</v>
       </c>
       <c r="E26">
-        <v>650.8</v>
+        <v>650.79999999999995</v>
       </c>
       <c r="G26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2607210031</v>
       </c>
@@ -1751,7 +1135,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2607210034</v>
       </c>
@@ -1771,7 +1155,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2607210036</v>
       </c>
@@ -1791,7 +1175,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2607210039</v>
       </c>
@@ -1811,7 +1195,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2607210040</v>
       </c>
@@ -1831,7 +1215,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9006</v>
       </c>
@@ -1851,7 +1235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1871,7 +1255,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2607210037</v>
       </c>
@@ -1891,7 +1275,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9007</v>
       </c>
@@ -1911,7 +1295,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2607210001</v>
       </c>
@@ -1934,7 +1318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2607210002</v>
       </c>
@@ -1957,7 +1341,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2607210004</v>
       </c>
@@ -1980,7 +1364,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2607210005</v>
       </c>
@@ -2003,7 +1387,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2607210007</v>
       </c>
@@ -2026,7 +1410,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2607210007</v>
       </c>
@@ -2049,7 +1433,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2607210008</v>
       </c>
@@ -2072,7 +1456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2607210009</v>
       </c>
@@ -2095,7 +1479,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2607210011</v>
       </c>
@@ -2118,7 +1502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2607210013</v>
       </c>
@@ -2141,7 +1525,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>42</v>
       </c>
@@ -2164,7 +1548,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>9008</v>
       </c>
@@ -2184,7 +1568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2607210001</v>
       </c>
@@ -2207,7 +1591,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2607210008</v>
       </c>
@@ -2230,7 +1614,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2607210009</v>
       </c>
@@ -2253,7 +1637,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2607210017</v>
       </c>
@@ -2276,7 +1660,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2607210030</v>
       </c>
@@ -2299,7 +1683,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2607210034</v>
       </c>
@@ -2322,7 +1706,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2607210039</v>
       </c>
@@ -2345,7 +1729,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2607210039</v>
       </c>
@@ -2368,7 +1752,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>9009</v>
       </c>
@@ -2388,7 +1772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2607210010</v>
       </c>
@@ -2411,7 +1795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>9011</v>
       </c>
@@ -2431,7 +1815,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>54</v>
       </c>
@@ -2451,7 +1835,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>54</v>
       </c>
@@ -2471,7 +1855,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2607210038</v>
       </c>
@@ -2491,7 +1875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2607210038</v>
       </c>
@@ -2511,7 +1895,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>9012</v>
       </c>
@@ -2531,7 +1915,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2607210001</v>
       </c>
@@ -2551,7 +1935,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2607210002</v>
       </c>
@@ -2571,7 +1955,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2607210008</v>
       </c>
@@ -2591,7 +1975,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2607210009</v>
       </c>
@@ -2611,7 +1995,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2607210009</v>
       </c>
@@ -2631,7 +2015,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2607210009</v>
       </c>
@@ -2651,7 +2035,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2607210009</v>
       </c>
@@ -2671,7 +2055,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2607210009</v>
       </c>
@@ -2691,7 +2075,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2607210010</v>
       </c>
@@ -2711,7 +2095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2607210011</v>
       </c>
@@ -2731,7 +2115,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2607210012</v>
       </c>
@@ -2751,7 +2135,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2607210020</v>
       </c>
@@ -2771,7 +2155,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2607210021</v>
       </c>
@@ -2791,7 +2175,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>62</v>
       </c>
@@ -2811,7 +2195,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>63</v>
       </c>
@@ -2831,7 +2215,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>64</v>
       </c>
@@ -2851,7 +2235,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>9019</v>
       </c>
@@ -2871,7 +2255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2607210001</v>
       </c>
@@ -2891,7 +2275,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2607210012</v>
       </c>
@@ -2911,7 +2295,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2607210015</v>
       </c>
@@ -2931,7 +2315,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>67</v>
       </c>
@@ -2949,7 +2333,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>